--- a/outputs/Sugar_percentile_classification_matrix.xlsx
+++ b/outputs/Sugar_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,76 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>32%</t>
+    <t>0%</t>
   </si>
 </sst>
 </file>
@@ -1108,10 +1039,10 @@
         <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE2" t="s">
         <v>108</v>
@@ -1135,28 +1066,28 @@
         <v>108</v>
       </c>
       <c r="AL2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT2" t="s">
         <v>108</v>
@@ -1240,13 +1171,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1311,13 +1242,13 @@
         <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
         <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
         <v>108</v>
@@ -1329,22 +1260,22 @@
         <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
         <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
         <v>108</v>
@@ -1362,43 +1293,43 @@
         <v>108</v>
       </c>
       <c r="AL3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY3" t="s">
         <v>108</v>
@@ -1467,13 +1398,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1556,19 +1487,19 @@
         <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
         <v>108</v>
@@ -1577,7 +1508,7 @@
         <v>108</v>
       </c>
       <c r="AH4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI4" t="s">
         <v>108</v>
@@ -1589,34 +1520,34 @@
         <v>108</v>
       </c>
       <c r="AL4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV4" t="s">
         <v>108</v>
@@ -1625,7 +1556,7 @@
         <v>108</v>
       </c>
       <c r="AX4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY4" t="s">
         <v>108</v>
@@ -1694,13 +1625,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1783,25 +1714,25 @@
         <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
         <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH5" t="s">
         <v>108</v>
@@ -1810,31 +1741,31 @@
         <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
         <v>108</v>
       </c>
       <c r="AL5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS5" t="s">
         <v>108</v>
@@ -1843,7 +1774,7 @@
         <v>108</v>
       </c>
       <c r="AU5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV5" t="s">
         <v>108</v>
@@ -1921,13 +1852,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1995,37 +1926,37 @@
         <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
         <v>108</v>
@@ -2043,34 +1974,34 @@
         <v>108</v>
       </c>
       <c r="AL6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s">
         <v>108</v>
       </c>
       <c r="AN6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT6" t="s">
         <v>108</v>
       </c>
       <c r="AU6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV6" t="s">
         <v>108</v>
@@ -2082,7 +2013,7 @@
         <v>108</v>
       </c>
       <c r="AY6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ6" t="s">
         <v>108</v>
@@ -2148,13 +2079,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2273,37 +2204,37 @@
         <v>108</v>
       </c>
       <c r="AM7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX7" t="s">
         <v>108</v>
@@ -2321,7 +2252,7 @@
         <v>108</v>
       </c>
       <c r="BC7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD7" t="s">
         <v>108</v>
@@ -2375,13 +2306,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2464,19 +2395,19 @@
         <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
         <v>108</v>
@@ -2497,49 +2428,49 @@
         <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW8" t="s">
         <v>108</v>
       </c>
       <c r="AX8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY8" t="s">
         <v>108</v>
       </c>
       <c r="AZ8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA8" t="s">
         <v>108</v>
@@ -2602,13 +2533,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2694,19 +2625,19 @@
         <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
         <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
         <v>108</v>
@@ -2724,43 +2655,43 @@
         <v>108</v>
       </c>
       <c r="AL9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY9" t="s">
         <v>108</v>
@@ -2769,7 +2700,7 @@
         <v>108</v>
       </c>
       <c r="BA9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB9" t="s">
         <v>108</v>
@@ -2829,13 +2760,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2900,10 +2831,10 @@
         <v>108</v>
       </c>
       <c r="U10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W10" t="s">
         <v>108</v>
@@ -2921,16 +2852,16 @@
         <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF10" t="s">
         <v>108</v>
@@ -2945,46 +2876,46 @@
         <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s">
         <v>108</v>
       </c>
       <c r="AL10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX10" t="s">
         <v>108</v>
@@ -3056,13 +2987,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3151,10 +3082,10 @@
         <v>108</v>
       </c>
       <c r="AC11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE11" t="s">
         <v>108</v>
@@ -3178,25 +3109,25 @@
         <v>108</v>
       </c>
       <c r="AL11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS11" t="s">
         <v>108</v>
@@ -3205,16 +3136,16 @@
         <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY11" t="s">
         <v>108</v>
@@ -3241,7 +3172,7 @@
         <v>108</v>
       </c>
       <c r="BG11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH11" t="s">
         <v>108</v>
@@ -3283,13 +3214,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3351,19 +3282,19 @@
         <v>108</v>
       </c>
       <c r="T12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="s">
         <v>108</v>
@@ -3372,19 +3303,19 @@
         <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
         <v>108</v>
@@ -3405,37 +3336,37 @@
         <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW12" t="s">
         <v>108</v>
@@ -3510,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3581,16 +3512,16 @@
         <v>108</v>
       </c>
       <c r="U13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
         <v>108</v>
@@ -3599,22 +3530,22 @@
         <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
         <v>108</v>
@@ -3632,43 +3563,43 @@
         <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW13" t="s">
         <v>108</v>
       </c>
       <c r="AX13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY13" t="s">
         <v>108</v>
@@ -3737,13 +3668,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3829,19 +3760,19 @@
         <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s">
         <v>108</v>
@@ -3859,25 +3790,25 @@
         <v>108</v>
       </c>
       <c r="AL14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS14" t="s">
         <v>108</v>
@@ -3886,16 +3817,16 @@
         <v>108</v>
       </c>
       <c r="AU14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY14" t="s">
         <v>108</v>
@@ -3964,13 +3895,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4038,10 +3969,10 @@
         <v>108</v>
       </c>
       <c r="V15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X15" t="s">
         <v>108</v>
@@ -4053,13 +3984,13 @@
         <v>108</v>
       </c>
       <c r="AA15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD15" t="s">
         <v>108</v>
@@ -4083,46 +4014,46 @@
         <v>108</v>
       </c>
       <c r="AK15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW15" t="s">
         <v>108</v>
       </c>
       <c r="AX15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY15" t="s">
         <v>108</v>
@@ -4131,7 +4062,7 @@
         <v>108</v>
       </c>
       <c r="BA15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB15" t="s">
         <v>108</v>
@@ -4191,13 +4122,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4262,10 +4193,10 @@
         <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W16" t="s">
         <v>108</v>
@@ -4280,19 +4211,19 @@
         <v>108</v>
       </c>
       <c r="AA16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
         <v>108</v>
@@ -4301,40 +4232,40 @@
         <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT16" t="s">
         <v>108</v>
@@ -4343,19 +4274,19 @@
         <v>108</v>
       </c>
       <c r="AV16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY16" t="s">
         <v>108</v>
       </c>
       <c r="AZ16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA16" t="s">
         <v>108</v>
@@ -4418,13 +4349,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4486,16 +4417,16 @@
         <v>108</v>
       </c>
       <c r="T17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X17" t="s">
         <v>108</v>
@@ -4507,22 +4438,22 @@
         <v>108</v>
       </c>
       <c r="AA17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s">
         <v>108</v>
@@ -4537,46 +4468,46 @@
         <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW17" t="s">
         <v>108</v>
       </c>
       <c r="AX17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY17" t="s">
         <v>108</v>
@@ -4645,13 +4576,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4716,13 +4647,13 @@
         <v>108</v>
       </c>
       <c r="U18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X18" t="s">
         <v>108</v>
@@ -4734,25 +4665,25 @@
         <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
         <v>108</v>
@@ -4767,49 +4698,49 @@
         <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW18" t="s">
         <v>108</v>
       </c>
       <c r="AX18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY18" t="s">
         <v>108</v>
       </c>
       <c r="AZ18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA18" t="s">
         <v>108</v>
@@ -4872,13 +4803,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4943,13 +4874,13 @@
         <v>108</v>
       </c>
       <c r="U19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X19" t="s">
         <v>108</v>
@@ -4961,22 +4892,22 @@
         <v>108</v>
       </c>
       <c r="AA19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG19" t="s">
         <v>108</v>
@@ -4997,40 +4928,40 @@
         <v>108</v>
       </c>
       <c r="AM19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
         <v>108</v>
@@ -5099,13 +5030,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5191,16 +5122,16 @@
         <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
         <v>108</v>
@@ -5221,25 +5152,25 @@
         <v>108</v>
       </c>
       <c r="AL20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS20" t="s">
         <v>108</v>
@@ -5248,19 +5179,19 @@
         <v>108</v>
       </c>
       <c r="AU20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW20" t="s">
         <v>108</v>
       </c>
       <c r="AX20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ20" t="s">
         <v>108</v>
@@ -5326,13 +5257,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5397,13 +5328,13 @@
         <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
         <v>108</v>
@@ -5415,22 +5346,22 @@
         <v>108</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
         <v>108</v>
@@ -5457,40 +5388,40 @@
         <v>108</v>
       </c>
       <c r="AO21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA21" t="s">
         <v>108</v>
@@ -5553,13 +5484,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5624,16 +5555,16 @@
         <v>108</v>
       </c>
       <c r="U22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W22" t="s">
         <v>108</v>
       </c>
       <c r="X22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s">
         <v>108</v>
@@ -5642,19 +5573,19 @@
         <v>108</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
         <v>108</v>
@@ -5678,40 +5609,40 @@
         <v>108</v>
       </c>
       <c r="AM22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY22" t="s">
         <v>108</v>
@@ -5780,13 +5711,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5851,10 +5782,10 @@
         <v>108</v>
       </c>
       <c r="U23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W23" t="s">
         <v>108</v>
@@ -5869,19 +5800,19 @@
         <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF23" t="s">
         <v>108</v>
@@ -5902,37 +5833,37 @@
         <v>108</v>
       </c>
       <c r="AL23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW23" t="s">
         <v>108</v>
@@ -6007,13 +5938,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6078,16 +6009,16 @@
         <v>108</v>
       </c>
       <c r="U24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y24" t="s">
         <v>108</v>
@@ -6099,19 +6030,19 @@
         <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG24" t="s">
         <v>108</v>
@@ -6132,49 +6063,49 @@
         <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ24" t="s">
         <v>108</v>
       </c>
       <c r="BA24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB24" t="s">
         <v>108</v>
@@ -6234,13 +6165,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6308,7 +6239,7 @@
         <v>108</v>
       </c>
       <c r="V25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W25" t="s">
         <v>108</v>
@@ -6320,19 +6251,19 @@
         <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
         <v>108</v>
@@ -6356,28 +6287,28 @@
         <v>108</v>
       </c>
       <c r="AL25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT25" t="s">
         <v>108</v>
@@ -6461,13 +6392,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6559,22 +6490,22 @@
         <v>108</v>
       </c>
       <c r="AD26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG26" t="s">
         <v>108</v>
       </c>
       <c r="AH26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ26" t="s">
         <v>108</v>
@@ -6583,34 +6514,34 @@
         <v>108</v>
       </c>
       <c r="AL26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS26" t="s">
         <v>108</v>
       </c>
       <c r="AT26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV26" t="s">
         <v>108</v>
@@ -6619,16 +6550,16 @@
         <v>108</v>
       </c>
       <c r="AX26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB26" t="s">
         <v>108</v>
@@ -6688,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6759,10 +6690,10 @@
         <v>108</v>
       </c>
       <c r="U27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W27" t="s">
         <v>108</v>
@@ -6777,22 +6708,22 @@
         <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
         <v>108</v>
@@ -6810,34 +6741,34 @@
         <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV27" t="s">
         <v>108</v>
@@ -6915,13 +6846,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6989,7 +6920,7 @@
         <v>108</v>
       </c>
       <c r="V28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W28" t="s">
         <v>108</v>
@@ -7004,22 +6935,22 @@
         <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
         <v>108</v>
@@ -7040,40 +6971,40 @@
         <v>108</v>
       </c>
       <c r="AM28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY28" t="s">
         <v>108</v>
@@ -7142,13 +7073,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7213,10 +7144,10 @@
         <v>108</v>
       </c>
       <c r="U29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W29" t="s">
         <v>108</v>
@@ -7234,19 +7165,19 @@
         <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="s">
         <v>108</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s">
         <v>108</v>
@@ -7264,37 +7195,37 @@
         <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW29" t="s">
         <v>108</v>
@@ -7369,13 +7300,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7440,10 +7371,10 @@
         <v>108</v>
       </c>
       <c r="U30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W30" t="s">
         <v>108</v>
@@ -7458,16 +7389,16 @@
         <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE30" t="s">
         <v>108</v>
@@ -7488,40 +7419,40 @@
         <v>108</v>
       </c>
       <c r="AK30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW30" t="s">
         <v>108</v>
@@ -7596,13 +7527,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7667,10 +7598,10 @@
         <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W31" t="s">
         <v>108</v>
@@ -7685,19 +7616,19 @@
         <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
         <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
         <v>108</v>
@@ -7712,31 +7643,31 @@
         <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS31" t="s">
         <v>108</v>
@@ -7745,16 +7676,16 @@
         <v>108</v>
       </c>
       <c r="AU31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV31" t="s">
         <v>108</v>
       </c>
       <c r="AW31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY31" t="s">
         <v>108</v>
@@ -7823,13 +7754,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7894,10 +7825,10 @@
         <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W32" t="s">
         <v>108</v>
@@ -7915,13 +7846,13 @@
         <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
         <v>108</v>
@@ -7939,28 +7870,28 @@
         <v>108</v>
       </c>
       <c r="AJ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR32" t="s">
         <v>108</v>
@@ -7975,13 +7906,13 @@
         <v>108</v>
       </c>
       <c r="AV32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY32" t="s">
         <v>108</v>
@@ -8050,13 +7981,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8121,7 +8052,7 @@
         <v>108</v>
       </c>
       <c r="U33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V33" t="s">
         <v>108</v>
@@ -8142,19 +8073,19 @@
         <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s">
         <v>108</v>
@@ -8166,49 +8097,49 @@
         <v>108</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY33" t="s">
         <v>108</v>
@@ -8277,13 +8208,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8348,13 +8279,13 @@
         <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X34" t="s">
         <v>108</v>
@@ -8363,22 +8294,22 @@
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
         <v>108</v>
@@ -8399,46 +8330,46 @@
         <v>108</v>
       </c>
       <c r="AL34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX34" t="s">
         <v>108</v>
       </c>
       <c r="AY34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ34" t="s">
         <v>108</v>
@@ -8504,13 +8435,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sugar_percentile_classification_matrix.xlsx
+++ b/outputs/Sugar_percentile_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
